--- a/flaskbackend/centercost_data/2025년10월.xlsx
+++ b/flaskbackend/centercost_data/2025년10월.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="271">
   <si>
     <t>코스트센터코드</t>
   </si>
@@ -827,9 +827,6 @@
   </si>
   <si>
     <t>(제)외주가공비-원자재</t>
-  </si>
-  <si>
-    <t>총비용</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E918"/>
+  <dimension ref="A1:E917"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16779,14 +16776,6 @@
         <v>21498590</v>
       </c>
     </row>
-    <row r="918" spans="1:5">
-      <c r="D918" t="s">
-        <v>271</v>
-      </c>
-      <c r="E918">
-        <v>8189539118</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
